--- a/database/event/4939/event_4939_evp_summary.xlsx
+++ b/database/event/4939/event_4939_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>4.0387</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8265</v>
+        <v>2.7591</v>
       </c>
       <c r="E2" t="n">
         <v>8.0398</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.8839</v>
+        <v>6.8808</v>
       </c>
       <c r="C3" t="n">
-        <v>3.458</v>
+        <v>3.4565</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3596</v>
+        <v>2.2974</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8839</v>
+        <v>6.8808</v>
       </c>
       <c r="F3" t="n">
-        <v>0.82</v>
+        <v>0.8169</v>
       </c>
       <c r="G3" t="n">
         <v>6.0639</v>
       </c>
       <c r="H3" t="n">
-        <v>0.82</v>
+        <v>0.8169</v>
       </c>
       <c r="I3" t="n">
         <v>0.8238</v>
@@ -594,7 +594,7 @@
         <v>3.0862</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0605</v>
+        <v>2.0037</v>
       </c>
       <c r="E4" t="n">
         <v>6.1436</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.7892</v>
+        <v>4.7868</v>
       </c>
       <c r="C5" t="n">
-        <v>2.4058</v>
+        <v>2.4046</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5134</v>
+        <v>1.4632</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7892</v>
+        <v>4.7868</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6459</v>
+        <v>0.6435</v>
       </c>
       <c r="G5" t="n">
         <v>4.1433</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6459</v>
+        <v>0.6435</v>
       </c>
       <c r="I5" t="n">
         <v>0.6489</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3677</v>
+        <v>4.3549</v>
       </c>
       <c r="C6" t="n">
-        <v>2.1941</v>
+        <v>2.1876</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3431</v>
+        <v>1.2911</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3677</v>
+        <v>4.3549</v>
       </c>
       <c r="F6" t="n">
-        <v>3.427</v>
+        <v>3.4142</v>
       </c>
       <c r="G6" t="n">
         <v>0.9407</v>
       </c>
       <c r="H6" t="n">
-        <v>3.427</v>
+        <v>3.4142</v>
       </c>
       <c r="I6" t="n">
         <v>3.4429</v>
@@ -732,7 +732,7 @@
         <v>2.12</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2835</v>
+        <v>1.2375</v>
       </c>
       <c r="E7" t="n">
         <v>4.2203</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0604</v>
+        <v>4.0494</v>
       </c>
       <c r="C8" t="n">
-        <v>2.0397</v>
+        <v>2.0342</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2189</v>
+        <v>1.1694</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0604</v>
+        <v>4.0494</v>
       </c>
       <c r="F8" t="n">
-        <v>2.955</v>
+        <v>2.944</v>
       </c>
       <c r="G8" t="n">
         <v>1.1054</v>
       </c>
       <c r="H8" t="n">
-        <v>2.955</v>
+        <v>2.944</v>
       </c>
       <c r="I8" t="n">
         <v>2.9688</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7998</v>
+        <v>3.7937</v>
       </c>
       <c r="C9" t="n">
-        <v>1.9088</v>
+        <v>1.9057</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1137</v>
+        <v>1.0675</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7998</v>
+        <v>3.7937</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6415</v>
+        <v>1.6354</v>
       </c>
       <c r="G9" t="n">
         <v>2.1583</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6415</v>
+        <v>1.6354</v>
       </c>
       <c r="I9" t="n">
         <v>1.6492</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.7094</v>
+        <v>3.6963</v>
       </c>
       <c r="C10" t="n">
-        <v>1.8634</v>
+        <v>1.8568</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0772</v>
+        <v>1.0287</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7094</v>
+        <v>3.6963</v>
       </c>
       <c r="F10" t="n">
-        <v>3.515</v>
+        <v>3.5019</v>
       </c>
       <c r="G10" t="n">
         <v>0.1944</v>
       </c>
       <c r="H10" t="n">
-        <v>3.515</v>
+        <v>3.5019</v>
       </c>
       <c r="I10" t="n">
         <v>3.5314</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.5721</v>
+        <v>3.558</v>
       </c>
       <c r="C11" t="n">
-        <v>1.7944</v>
+        <v>1.7873</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0217</v>
+        <v>0.9736</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5721</v>
+        <v>3.558</v>
       </c>
       <c r="F11" t="n">
-        <v>3.7734</v>
+        <v>3.7593</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2013</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7734</v>
+        <v>3.7593</v>
       </c>
       <c r="I11" t="n">
         <v>3.7909</v>
@@ -962,7 +962,7 @@
         <v>1.7598</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9939</v>
+        <v>0.9518</v>
       </c>
       <c r="E12" t="n">
         <v>3.5032</v>
@@ -1008,7 +1008,7 @@
         <v>1.6548</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9094</v>
+        <v>0.8685</v>
       </c>
       <c r="E13" t="n">
         <v>3.2942</v>
@@ -1054,7 +1054,7 @@
         <v>1.6239</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8845</v>
+        <v>0.844</v>
       </c>
       <c r="E14" t="n">
         <v>3.2326</v>
@@ -1100,7 +1100,7 @@
         <v>1.5232</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8036</v>
+        <v>0.7641</v>
       </c>
       <c r="E15" t="n">
         <v>3.0322</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.8305</v>
+        <v>2.8236</v>
       </c>
       <c r="C16" t="n">
-        <v>1.4219</v>
+        <v>1.4184</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7221</v>
+        <v>0.681</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8305</v>
+        <v>2.8236</v>
       </c>
       <c r="F16" t="n">
-        <v>1.85</v>
+        <v>1.8431</v>
       </c>
       <c r="G16" t="n">
         <v>0.9805</v>
       </c>
       <c r="H16" t="n">
-        <v>1.85</v>
+        <v>1.8431</v>
       </c>
       <c r="I16" t="n">
         <v>1.8586</v>
@@ -1192,7 +1192,7 @@
         <v>1.3967</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7019</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="E17" t="n">
         <v>2.7805</v>
@@ -1238,7 +1238,7 @@
         <v>1.3758</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6851</v>
+        <v>0.6472</v>
       </c>
       <c r="E18" t="n">
         <v>2.7388</v>
@@ -1284,7 +1284,7 @@
         <v>1.3406</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.6193</v>
       </c>
       <c r="E19" t="n">
         <v>2.6688</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.6234</v>
+        <v>2.6164</v>
       </c>
       <c r="C20" t="n">
-        <v>1.3178</v>
+        <v>1.3143</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6384</v>
+        <v>0.5985</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6234</v>
+        <v>2.6164</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8711</v>
+        <v>1.8641</v>
       </c>
       <c r="G20" t="n">
         <v>0.7523</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8711</v>
+        <v>1.8641</v>
       </c>
       <c r="I20" t="n">
         <v>1.8798</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.5942</v>
+        <v>2.591</v>
       </c>
       <c r="C21" t="n">
-        <v>1.3032</v>
+        <v>1.3016</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6266</v>
+        <v>0.5883</v>
       </c>
       <c r="E21" t="n">
-        <v>2.5942</v>
+        <v>2.591</v>
       </c>
       <c r="F21" t="n">
-        <v>0.879</v>
+        <v>0.8758</v>
       </c>
       <c r="G21" t="n">
         <v>1.7152</v>
       </c>
       <c r="H21" t="n">
-        <v>0.879</v>
+        <v>0.8758</v>
       </c>
       <c r="I21" t="n">
         <v>0.8831</v>
@@ -1422,7 +1422,7 @@
         <v>1.2933</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6187</v>
+        <v>0.5818</v>
       </c>
       <c r="E22" t="n">
         <v>2.5746</v>
@@ -1468,7 +1468,7 @@
         <v>1.2492</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5468</v>
       </c>
       <c r="E23" t="n">
         <v>2.4867</v>
@@ -1514,7 +1514,7 @@
         <v>1.2007</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5442</v>
+        <v>0.5083</v>
       </c>
       <c r="E24" t="n">
         <v>2.3902</v>
@@ -1560,7 +1560,7 @@
         <v>1.1048</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4671</v>
+        <v>0.4323</v>
       </c>
       <c r="E25" t="n">
         <v>2.1993</v>
@@ -1606,7 +1606,7 @@
         <v>1.0264</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4041</v>
+        <v>0.3701</v>
       </c>
       <c r="E26" t="n">
         <v>2.0433</v>
@@ -1652,7 +1652,7 @@
         <v>1.0024</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3847</v>
+        <v>0.3511</v>
       </c>
       <c r="E27" t="n">
         <v>1.9954</v>
@@ -1698,7 +1698,7 @@
         <v>0.9714</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3599</v>
+        <v>0.3265</v>
       </c>
       <c r="E28" t="n">
         <v>1.9338</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.8958</v>
+        <v>1.8838</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9523</v>
+        <v>0.9463</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3445</v>
+        <v>0.3066</v>
       </c>
       <c r="E29" t="n">
-        <v>1.8958</v>
+        <v>1.8838</v>
       </c>
       <c r="F29" t="n">
-        <v>3.22</v>
+        <v>3.208</v>
       </c>
       <c r="G29" t="n">
         <v>-1.3242</v>
       </c>
       <c r="H29" t="n">
-        <v>3.22</v>
+        <v>3.208</v>
       </c>
       <c r="I29" t="n">
         <v>3.235</v>
@@ -1790,7 +1790,7 @@
         <v>0.9173</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3163</v>
+        <v>0.2836</v>
       </c>
       <c r="E30" t="n">
         <v>1.826</v>
@@ -1836,7 +1836,7 @@
         <v>0.9133</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3131</v>
+        <v>0.2804</v>
       </c>
       <c r="E31" t="n">
         <v>1.8181</v>
@@ -1882,7 +1882,7 @@
         <v>0.911</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3113</v>
+        <v>0.2786</v>
       </c>
       <c r="E32" t="n">
         <v>1.8136</v>
@@ -1928,7 +1928,7 @@
         <v>0.8718</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2797</v>
+        <v>0.2475</v>
       </c>
       <c r="E33" t="n">
         <v>1.7355</v>
@@ -1974,7 +1974,7 @@
         <v>0.7942</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2174</v>
+        <v>0.186</v>
       </c>
       <c r="E34" t="n">
         <v>1.5811</v>
@@ -2020,7 +2020,7 @@
         <v>0.7917</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2153</v>
+        <v>0.184</v>
       </c>
       <c r="E35" t="n">
         <v>1.5761</v>
@@ -2066,7 +2066,7 @@
         <v>0.7748</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2017</v>
+        <v>0.1706</v>
       </c>
       <c r="E36" t="n">
         <v>1.5424</v>
@@ -2112,7 +2112,7 @@
         <v>0.7659</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1945</v>
+        <v>0.1635</v>
       </c>
       <c r="E37" t="n">
         <v>1.5246</v>
@@ -2158,7 +2158,7 @@
         <v>0.6425999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0954</v>
+        <v>0.0658</v>
       </c>
       <c r="E38" t="n">
         <v>1.2793</v>
@@ -2204,7 +2204,7 @@
         <v>0.5504</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0212</v>
+        <v>-0.0074</v>
       </c>
       <c r="E39" t="n">
         <v>1.0956</v>
@@ -2250,7 +2250,7 @@
         <v>0.5074</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0133</v>
+        <v>-0.0415</v>
       </c>
       <c r="E40" t="n">
         <v>1.01</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9946</v>
+        <v>0.9923</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4996</v>
+        <v>0.4985</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0196</v>
+        <v>-0.0486</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9946</v>
+        <v>0.9923</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.6212</v>
       </c>
       <c r="G41" t="n">
         <v>0.3711</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.6212</v>
       </c>
       <c r="I41" t="n">
         <v>0.6264</v>
@@ -2342,7 +2342,7 @@
         <v>0.3395</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1483</v>
+        <v>-0.1746</v>
       </c>
       <c r="E42" t="n">
         <v>0.6758999999999999</v>
@@ -2388,7 +2388,7 @@
         <v>0.2895</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1885</v>
+        <v>-0.2143</v>
       </c>
       <c r="E43" t="n">
         <v>0.5764</v>
@@ -2434,7 +2434,7 @@
         <v>0.2768</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1987</v>
+        <v>-0.2244</v>
       </c>
       <c r="E44" t="n">
         <v>0.5511</v>
@@ -2480,7 +2480,7 @@
         <v>0.2743</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2007</v>
+        <v>-0.2263</v>
       </c>
       <c r="E45" t="n">
         <v>0.5461</v>
@@ -2526,7 +2526,7 @@
         <v>0.2678</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.206</v>
+        <v>-0.2315</v>
       </c>
       <c r="E46" t="n">
         <v>0.5332</v>
@@ -2572,7 +2572,7 @@
         <v>0.2667</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2069</v>
+        <v>-0.2324</v>
       </c>
       <c r="E47" t="n">
         <v>0.531</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4767</v>
+        <v>0.4729</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2395</v>
+        <v>0.2376</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2288</v>
+        <v>-0.2555</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4767</v>
+        <v>0.4729</v>
       </c>
       <c r="F48" t="n">
-        <v>1.0283</v>
+        <v>1.0245</v>
       </c>
       <c r="G48" t="n">
         <v>-0.5516</v>
       </c>
       <c r="H48" t="n">
-        <v>1.0283</v>
+        <v>1.0245</v>
       </c>
       <c r="I48" t="n">
         <v>1.0331</v>
@@ -2664,7 +2664,7 @@
         <v>0.1908</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2679</v>
+        <v>-0.2926</v>
       </c>
       <c r="E49" t="n">
         <v>0.3799</v>
@@ -2710,7 +2710,7 @@
         <v>0.1903</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2683</v>
+        <v>-0.293</v>
       </c>
       <c r="E50" t="n">
         <v>0.3789</v>
@@ -2756,7 +2756,7 @@
         <v>0.1556</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.2962</v>
+        <v>-0.3205</v>
       </c>
       <c r="E51" t="n">
         <v>0.3098</v>
@@ -2802,7 +2802,7 @@
         <v>0.0577</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.375</v>
+        <v>-0.3982</v>
       </c>
       <c r="E52" t="n">
         <v>0.1148</v>
@@ -2848,7 +2848,7 @@
         <v>0.0064</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4162</v>
+        <v>-0.4388</v>
       </c>
       <c r="E53" t="n">
         <v>0.0128</v>
@@ -2894,7 +2894,7 @@
         <v>-0.0109</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4301</v>
+        <v>-0.4525</v>
       </c>
       <c r="E54" t="n">
         <v>-0.0216</v>
@@ -2940,7 +2940,7 @@
         <v>-0.0111</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4303</v>
+        <v>-0.4527</v>
       </c>
       <c r="E55" t="n">
         <v>-0.0221</v>
@@ -2986,7 +2986,7 @@
         <v>-0.028</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4439</v>
+        <v>-0.4661</v>
       </c>
       <c r="E56" t="n">
         <v>-0.0558</v>
@@ -3032,7 +3032,7 @@
         <v>-0.0555</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.466</v>
+        <v>-0.4879</v>
       </c>
       <c r="E57" t="n">
         <v>-0.1104</v>
@@ -3078,7 +3078,7 @@
         <v>-0.1157</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5144</v>
+        <v>-0.5357</v>
       </c>
       <c r="E58" t="n">
         <v>-0.2303</v>
@@ -3124,7 +3124,7 @@
         <v>-0.1159</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="E59" t="n">
         <v>-0.2307</v>
@@ -3170,7 +3170,7 @@
         <v>-0.13</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5259</v>
+        <v>-0.547</v>
       </c>
       <c r="E60" t="n">
         <v>-0.2588</v>
@@ -3216,7 +3216,7 @@
         <v>-0.1524</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.5648</v>
       </c>
       <c r="E61" t="n">
         <v>-0.3034</v>
@@ -3262,7 +3262,7 @@
         <v>-0.2431</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6168</v>
+        <v>-0.6367</v>
       </c>
       <c r="E62" t="n">
         <v>-0.4839</v>
@@ -3308,7 +3308,7 @@
         <v>-0.2995</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6623</v>
+        <v>-0.6815</v>
       </c>
       <c r="E63" t="n">
         <v>-0.5963000000000001</v>
@@ -3354,7 +3354,7 @@
         <v>-0.34</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6948</v>
+        <v>-0.7136</v>
       </c>
       <c r="E64" t="n">
         <v>-0.6768999999999999</v>
@@ -3400,7 +3400,7 @@
         <v>-0.3499</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7028</v>
+        <v>-0.7214</v>
       </c>
       <c r="E65" t="n">
         <v>-0.6966</v>
@@ -3446,7 +3446,7 @@
         <v>-0.4199</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.759</v>
+        <v>-0.7769</v>
       </c>
       <c r="E66" t="n">
         <v>-0.8358</v>
@@ -3492,7 +3492,7 @@
         <v>-0.4419</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.7943</v>
       </c>
       <c r="E67" t="n">
         <v>-0.8796</v>
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.0218</v>
+        <v>-1.0227</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5133</v>
+        <v>-0.5137</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8341</v>
+        <v>-0.8514</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.0218</v>
+        <v>-1.0227</v>
       </c>
       <c r="F68" t="n">
-        <v>0.2329</v>
+        <v>0.232</v>
       </c>
       <c r="G68" t="n">
         <v>-1.2547</v>
       </c>
       <c r="H68" t="n">
-        <v>0.2329</v>
+        <v>0.232</v>
       </c>
       <c r="I68" t="n">
         <v>0.234</v>
@@ -3584,7 +3584,7 @@
         <v>-0.5825</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8898</v>
+        <v>-0.9059</v>
       </c>
       <c r="E69" t="n">
         <v>-1.1596</v>
@@ -3630,7 +3630,7 @@
         <v>-0.5908</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8965</v>
+        <v>-0.9125</v>
       </c>
       <c r="E70" t="n">
         <v>-1.1762</v>
@@ -3676,7 +3676,7 @@
         <v>-0.6302</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9282</v>
+        <v>-0.9437</v>
       </c>
       <c r="E71" t="n">
         <v>-1.2546</v>
@@ -3722,7 +3722,7 @@
         <v>-0.6747</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9639</v>
+        <v>-0.979</v>
       </c>
       <c r="E72" t="n">
         <v>-1.3431</v>
@@ -3768,7 +3768,7 @@
         <v>-0.7057</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9889</v>
+        <v>-1.0036</v>
       </c>
       <c r="E73" t="n">
         <v>-1.4048</v>
@@ -3814,7 +3814,7 @@
         <v>-0.7175</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9984</v>
+        <v>-1.0129</v>
       </c>
       <c r="E74" t="n">
         <v>-1.4283</v>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.7942</v>
+        <v>-1.7896</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.9013</v>
+        <v>-0.899</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1462</v>
+        <v>-1.1569</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.7942</v>
+        <v>-1.7896</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.2305</v>
+        <v>-1.2259</v>
       </c>
       <c r="G75" t="n">
         <v>-0.5637</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.2305</v>
+        <v>-1.2259</v>
       </c>
       <c r="I75" t="n">
         <v>-1.2362</v>
@@ -3906,7 +3906,7 @@
         <v>-0.9411</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1782</v>
+        <v>-1.1903</v>
       </c>
       <c r="E76" t="n">
         <v>-1.8735</v>
@@ -3952,7 +3952,7 @@
         <v>-0.9461000000000001</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1822</v>
+        <v>-1.1943</v>
       </c>
       <c r="E77" t="n">
         <v>-1.8834</v>
@@ -3998,7 +3998,7 @@
         <v>-0.9825</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2115</v>
+        <v>-1.2231</v>
       </c>
       <c r="E78" t="n">
         <v>-1.9558</v>
@@ -4044,7 +4044,7 @@
         <v>-1.0047</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E79" t="n">
         <v>-2</v>
@@ -4090,7 +4090,7 @@
         <v>-1.0891</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.2972</v>
+        <v>-1.3077</v>
       </c>
       <c r="E80" t="n">
         <v>-2.1681</v>
@@ -4136,7 +4136,7 @@
         <v>-1.3156</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.4793</v>
+        <v>-1.4873</v>
       </c>
       <c r="E81" t="n">
         <v>-2.6189</v>
